--- a/output/laminas_provinciales/prov_i_ingr_a_2018_biobio.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2018_biobio.xlsx
@@ -454,7 +454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -478,6 +478,13 @@
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Concepción</t>
         </is>
